--- a/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
@@ -751,7 +751,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1079,10 +1079,8 @@
           <t>Roshan Shrestha</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9700971170</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9700971170</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -1172,25 +1170,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>1,15</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.33794</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.33794</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : worst internet service   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,36 +528,54 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -572,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -628,7 +646,30 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -643,12 +684,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -659,10 +701,15 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -671,27 +718,49 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C4" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -705,11 +774,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX2"/>
+  <dimension ref="A1:AX3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -742,7 +811,7 @@
     <col width="22" customWidth="1" min="32" max="32"/>
     <col width="29" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
-    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="13" customWidth="1" min="38" max="38"/>
@@ -751,7 +820,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1218,6 +1287,210 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 10:23 AM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 router</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351764</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Bardan  Rai</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Bardan  Rai</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>9801888651</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 10:23:44 AM</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>9840534105</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:19:29 PM</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 10:23:44 AM</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr">
+        <is>
+          <t>Request</t>
+        </is>
+      </c>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>Aarubari Chowk Bus Stop - Bus stop Gokarneshwor 4460, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr"/>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>23:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr"/>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>L36-8</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>2d 17h 4m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
@@ -562,18 +562,36 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
@@ -634,14 +652,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -657,14 +675,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -684,13 +702,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -711,6 +730,11 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>Grand Total</t>
         </is>
       </c>
@@ -725,42 +749,70 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="6" t="n">
-        <v>1</v>
+      <c r="E2" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="E3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="4" t="n">
-        <v>2</v>
+      <c r="E5" s="4" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -774,7 +826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX3"/>
+  <dimension ref="A1:AX5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -792,7 +844,7 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="27" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -802,19 +854,19 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="27" customWidth="1" min="26" max="26"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="22" customWidth="1" min="32" max="32"/>
+    <col width="29" customWidth="1" min="32" max="32"/>
     <col width="29" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="13" customWidth="1" min="38" max="38"/>
+    <col width="14" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -1354,10 +1406,8 @@
           <t>Bardan  Rai</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9801888651</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9801888651</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1443,10 +1493,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
@@ -1457,29 +1505,29 @@
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>2d 17h 4m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6 router  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS3" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT3" s="3" t="inlineStr">
-        <is>
-          <t>2d 17h 4m</t>
-        </is>
-      </c>
-      <c r="AU3" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV3" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 router  has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="AW3" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -1488,6 +1536,434 @@
       <c r="AX3" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 10:46 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1354797</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Shreyak Timsina</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Shreyak Timsina</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9863626262</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 09:20:39 AM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>9863626262</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 09:20:39 AM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 10:46:47 AM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>27.691212</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>M8RF+FCM, Radha Krishna Marg, Kathmandu 44600,Department of Commerce, Supplies and Consumer Protecti</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>shreyaktimsina29@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr"/>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>L63-4</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>85.323547</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>1h 26m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>1h 26m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 10:33 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : CONFINGURE ISSUE  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>CONFINGURE ISSUE</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353468</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Bigyan Shrestha</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Bigyan Shrestha</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9746458564</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 10:18:34 AM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9813031745</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 07:30:42 AM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 10:33:35 AM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>27.68067</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu Matatirtha Mahalaxmi school, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>stha.bigyan03@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>10:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Sanam Sadar</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>CDB348</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>85.23175</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : CONFINGURE ISSUE  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>1d 15m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 2m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : CONFINGURE ISSUE  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -664,30 +664,53 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>WiFi 6 Upgrade</t>
+          <t>IPTV Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -702,10 +725,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -780,14 +803,14 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0</v>
@@ -797,22 +820,41 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>4</v>
+      <c r="E6" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -826,7 +868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX5"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -861,12 +903,12 @@
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
     <col width="29" customWidth="1" min="32" max="32"/>
-    <col width="29" customWidth="1" min="33" max="33"/>
+    <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="14" customWidth="1" min="38" max="38"/>
+    <col width="16" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -1606,10 +1648,8 @@
           <t>Shreyak Timsina</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9863626262</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9863626262</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1699,25 +1739,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>L63-4</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>85.323547</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>85.323547</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
@@ -1818,10 +1854,8 @@
           <t>Bigyan Shrestha</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9746458564</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9746458564</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1915,47 +1949,43 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>CDB348</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.23175</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>85.23175000000001</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>1d 15m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 2m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
           <t>Case : CONFINGURE ISSUE  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS5" s="3" t="inlineStr">
-        <is>
-          <t>1d 15m</t>
-        </is>
-      </c>
-      <c r="AT5" s="3" t="inlineStr">
-        <is>
-          <t>1d 3h 2m</t>
-        </is>
-      </c>
-      <c r="AU5" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV5" s="3" t="inlineStr">
-        <is>
-          <t>Case : CONFINGURE ISSUE  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW5" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -1964,6 +1994,222 @@
       <c r="AX5" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 10:56 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV issue</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353850</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Saila aryal</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Saila aryal</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9841360381</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 10:56:58 AM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9841360381</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:19:12 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 10:56:58 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>27.726752</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>near Bodhi Guest House ,27.72596, 85.36072 27.72596, 85.36072 saraswatinagar RD, Bagmati, Central, N</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>pramod.karki2016@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>08:37 hour</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Bhawana Bista</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>L45-6</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>85.360973</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>22h 37m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,14 +528,14 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Sabin Giri</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -546,54 +546,72 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Sunil Chaudhary</t>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>60.0%</t>
+      <c r="B6" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -652,19 +670,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
           <t>50.0%</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -687,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -710,7 +728,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -725,14 +743,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -743,20 +762,25 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -769,45 +793,51 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="F2" s="6" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Channel buffering,feeze issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
@@ -815,14 +845,17 @@
       <c r="D4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -834,27 +867,55 @@
       <c r="D5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="D7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="E7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>5</v>
+      <c r="F7" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -868,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX6"/>
+  <dimension ref="A1:AX7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -881,10 +942,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -908,7 +969,7 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="18" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -2064,10 +2125,8 @@
           <t>Saila aryal</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9841360381</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9841360381</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -2161,55 +2220,263 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>L45-6</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>85.360973</t>
-        </is>
+      <c r="AP6" s="3" t="n">
+        <v>85.360973</v>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>22h 37m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
           <t>Case : IPTV issue   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS6" s="3" t="inlineStr">
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 11:07 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g name not showing   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>5g name not showing</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353810</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Chandar Bahadur Tamang</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Chandar Bahadur Tamang</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9841602946</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 11:07:12 AM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9841602946</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:50:35 AM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 11:07:12 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>27.66861</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Nearest Dragon Bakery Details from Google Maps M89F+HFH, Prayag Pokhari Marg, Lalitpur 44600 +977 1-</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr"/>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>09:17 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Nirmaya Mukhiya</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>4,10</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>85.32358</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g name not showing   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT6" s="3" t="inlineStr">
-        <is>
-          <t>22h 37m</t>
-        </is>
-      </c>
-      <c r="AU6" s="3" t="inlineStr">
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>23h 16m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV6" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV issue   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW6" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
-        </is>
-      </c>
-      <c r="AX6" s="3" t="inlineStr">
-        <is>
-          <t>Sabin Giri</t>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g name not showing   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -716,19 +716,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -802,10 +802,10 @@
         <v>1</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -833,20 +833,20 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>1</v>
@@ -855,20 +855,20 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Channel buffering,feeze issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>1</v>
@@ -877,17 +877,17 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
@@ -897,25 +897,47 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="E8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>6</v>
+      <c r="F8" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -929,7 +951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX7"/>
+  <dimension ref="A1:AX9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -942,10 +964,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -2335,10 +2357,8 @@
           <t>Chandar Bahadur Tamang</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9841602946</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9841602946</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -2428,47 +2448,43 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>4,10</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>85.32358</t>
-        </is>
+      <c r="AP7" s="3" t="n">
+        <v>85.32358000000001</v>
       </c>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>23h 16m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
           <t>Case : 5g name not showing   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS7" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT7" s="3" t="inlineStr">
-        <is>
-          <t>23h 16m</t>
-        </is>
-      </c>
-      <c r="AU7" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV7" s="3" t="inlineStr">
-        <is>
-          <t>Case : 5g name not showing   has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
       <c r="AW7" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -2477,6 +2493,322 @@
       <c r="AX7" s="3" t="inlineStr">
         <is>
           <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 11:27 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr"/>
+      <c r="N8" s="3" t="inlineStr"/>
+      <c r="O8" s="3" t="inlineStr"/>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr"/>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr"/>
+      <c r="V8" s="3" t="inlineStr"/>
+      <c r="W8" s="3" t="inlineStr"/>
+      <c r="X8" s="3" t="inlineStr"/>
+      <c r="Y8" s="3" t="inlineStr"/>
+      <c r="Z8" s="3" t="inlineStr"/>
+      <c r="AA8" s="3" t="inlineStr"/>
+      <c r="AB8" s="3" t="inlineStr"/>
+      <c r="AC8" s="3" t="inlineStr"/>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr"/>
+      <c r="AF8" s="3" t="inlineStr"/>
+      <c r="AG8" s="3" t="inlineStr"/>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr"/>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr"/>
+      <c r="AM8" s="3" t="inlineStr"/>
+      <c r="AN8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr"/>
+      <c r="AP8" s="3" t="inlineStr"/>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX8" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 11:24 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>WIFI 6</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1354160</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Mandira Karanjti Shrestha</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Mandira Karanjti Shrestha</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9761809898</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:20:57 PM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9761809898</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:20:57 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 11:24:23 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Gurjudhara Chandragiri 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>shresthakapil478@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>05:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>CDB087</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>19h 3m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>19h 3m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -670,19 +670,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>10.0%</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>30.0%</t>
         </is>
       </c>
     </row>
@@ -811,11 +811,11 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
@@ -824,10 +824,10 @@
         <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -855,11 +855,11 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -868,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>1</v>
@@ -934,10 +934,10 @@
         <v>2</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -951,7 +951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX9"/>
+  <dimension ref="A1:AX11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -974,7 +974,7 @@
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
@@ -991,7 +991,7 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="18" customWidth="1" min="38" max="38"/>
+    <col width="28" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -2671,10 +2671,8 @@
           <t>Mandira Karanjti Shrestha</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9761809898</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9761809898</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2764,10 +2762,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
@@ -2778,35 +2774,459 @@
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>19h 3m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>19h 3m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
           <t>Case : WIFI 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS9" s="3" t="inlineStr">
-        <is>
-          <t>19h 3m</t>
-        </is>
-      </c>
-      <c r="AT9" s="3" t="inlineStr">
-        <is>
-          <t>19h 3m</t>
-        </is>
-      </c>
-      <c r="AU9" s="3" t="inlineStr">
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 11:42 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : no  light in router   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>no  light in router</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1354771</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Dhan Bahadur Lama</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Dhan Bahadur Lama</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9846051876</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 08:48:10 AM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>PKR9846051876</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 08:43:43 AM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 11:42:33 AM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>28.208549</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>27.693034673347515, 85.22407912559657 GPS Coordinates Nearest: CDB152 (57m Road) Map: CG Satungal, G</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr"/>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>01:41 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Yadav (L1 Support)</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>CDB152</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>83.993742</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : no  light in router   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>2h 54m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>2h 58m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV9" s="3" t="inlineStr">
-        <is>
-          <t>Case : WIFI 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW9" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
-        </is>
-      </c>
-      <c r="AX9" s="3" t="inlineStr">
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : no  light in router   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX10" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 11:41 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : no  light in router   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>no  light in router</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1354771</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Dhan Bahadur Lama</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Dhan Bahadur Lama</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9846051876</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 08:48:10 AM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>PKR9846051876</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 08:43:43 AM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 11:42:33 AM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>28.208549</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>27.693034673347515, 85.22407912559657 GPS Coordinates Nearest: CDB152 (57m Road) Map: CG Satungal, G</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr"/>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>01:41 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Yadav (L1 Support)</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>CDB152</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>83.993742</t>
+        </is>
+      </c>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : no  light in router   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>2h 54m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>2h 58m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : no  light in router   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX11" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Rajesh Maharjan</t>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -546,72 +546,90 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Sabin Giri</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Sunil Chaudhary</t>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B7" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="C7" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="C6" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>70.0%</t>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -670,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
     </row>
@@ -693,10 +711,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -705,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>15.4%</t>
         </is>
       </c>
     </row>
@@ -716,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
     </row>
@@ -743,15 +761,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -762,25 +781,30 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -804,8 +828,11 @@
       <c r="E2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="6" t="n">
-        <v>3</v>
+      <c r="F2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -824,60 +851,69 @@
         <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="G3" s="6" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="6" t="n">
-        <v>1</v>
+      <c r="G4" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Channel buffering,feeze issue</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -892,14 +928,17 @@
       <c r="E6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -914,30 +953,61 @@
       <c r="E7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" s="4" t="n">
+      <c r="E9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="4" t="n">
-        <v>9</v>
+      <c r="F9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -951,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX11"/>
+  <dimension ref="A1:AX14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -980,7 +1050,7 @@
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
@@ -2875,10 +2945,8 @@
           <t>Dhan Bahadur Lama</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9846051876</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9846051876</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2968,25 +3036,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>CDB152</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>83.993742</t>
-        </is>
+      <c r="AP10" s="3" t="n">
+        <v>83.993742</v>
       </c>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : no  light in router   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
@@ -3087,10 +3151,8 @@
           <t>Dhan Bahadur Lama</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9846051876</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9846051876</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -3180,47 +3242,43 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>CDB152</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>83.993742</t>
-        </is>
+      <c r="AP11" s="3" t="n">
+        <v>83.993742</v>
       </c>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>2h 54m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>2h 58m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
           <t>Case : no  light in router   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS11" s="3" t="inlineStr">
-        <is>
-          <t>2h 54m</t>
-        </is>
-      </c>
-      <c r="AT11" s="3" t="inlineStr">
-        <is>
-          <t>2h 58m</t>
-        </is>
-      </c>
-      <c r="AU11" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV11" s="3" t="inlineStr">
-        <is>
-          <t>Case : no  light in router   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW11" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -3229,6 +3287,654 @@
       <c r="AX11" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 11:57 AM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>IPTV issue</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353054</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Umesh Thakur</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Umesh Thakur</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9805889944</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 11:57:41 AM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>BKT9805889944</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 05:32:23 PM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 11:57:41 AM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.659463</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Changathali, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>test@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>14:25 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Naman Mallik</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>2,10</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.359684</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 25m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX12" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 11:59 AM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : TV setup box   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>TV setup box</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353686</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Kiran Shrestha</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Kiran Shrestha</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9841308494</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 11:59:16 AM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>9841308494</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 10:41:06 AM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 11:59:16 AM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>27.7045</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-customer care</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>Namuna E.B. School, Chwas Pakha Marg, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>shrestha100kiran@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>11:18 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr"/>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>4,13</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>85.30243</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : TV setup box   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 18m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : TV setup box   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX13" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 11:48 AM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341380</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Aama Milan Kendra</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Aama Milan Kendra</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9851220331</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 11:48:06 AM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9841863259</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 02:06:54 PM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 11:48:06 AM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>27.6907</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Chakrabarti Habi Education Academy College of Law,Bijulibazar, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>01:42 hour</t>
+        </is>
+      </c>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>L48-6</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>85.32893</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>10d 21h 41m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX14" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>1</v>
@@ -832,7 +832,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -998,7 +998,7 @@
         <v>2</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>3</v>
@@ -1007,7 +1007,7 @@
         <v>3</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1021,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX14"/>
+  <dimension ref="A1:AX15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3347,20 +3347,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M12" s="3" t="inlineStr"/>
       <c r="N12" s="3" t="inlineStr">
         <is>
           <t>Umesh Thakur</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9805889944</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9805889944</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -3454,25 +3448,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>2,10</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.359684</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.359684</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV issue  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
@@ -3573,10 +3563,8 @@
           <t>Kiran Shrestha</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9841308494</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9841308494</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3670,25 +3658,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>4,13</t>
         </is>
       </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>85.30243</t>
-        </is>
+      <c r="AP13" s="3" t="n">
+        <v>85.30243</v>
       </c>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>Case : TV setup box   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
@@ -3789,10 +3773,8 @@
           <t>Aama Milan Kendra</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9851220331</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9851220331</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3886,55 +3868,259 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>L48-6</t>
         </is>
       </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>85.32893</t>
-        </is>
+      <c r="AP14" s="3" t="n">
+        <v>85.32893</v>
       </c>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>10d 21h 41m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS14" s="3" t="inlineStr">
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX14" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 12:03 PM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1354108</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Nagendra Prasad Yadav</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Nagendra Prasad Yadav</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9808532673</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 12:03:11 PM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>CHB9808532673</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:42:41 PM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 12:03:11 PM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr"/>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>27.70495252716337, 85.34485820675248, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr">
+        <is>
+          <t>9808532673@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>06:21 hour</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>L43-5</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr"/>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT14" s="3" t="inlineStr">
-        <is>
-          <t>10d 21h 41m</t>
-        </is>
-      </c>
-      <c r="AU14" s="3" t="inlineStr">
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>20h 20m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV14" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW14" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
-        </is>
-      </c>
-      <c r="AX14" s="3" t="inlineStr">
-        <is>
-          <t>Rajesh Maharjan</t>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX15" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>13.3%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>1</v>
@@ -832,7 +832,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -998,7 +998,7 @@
         <v>2</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>3</v>
@@ -1007,7 +1007,7 @@
         <v>3</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1021,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX15"/>
+  <dimension ref="A1:AX16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3983,10 +3983,8 @@
           <t>Nagendra Prasad Yadav</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9808532673</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9808532673</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -4076,10 +4074,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
@@ -4090,35 +4086,251 @@
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>20h 20m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
           <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS15" s="3" t="inlineStr">
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX15" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 12:27 PM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1354735</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Divesh Mainali</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Divesh Mainali</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9849444217</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 12:27:52 PM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>9849444217</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 07:46:33 AM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 12:27:52 PM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>27.69906</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Near to Bishranti Catering Service &amp; Party Palace Pvt.ltd.,Omnagar Marg, Kathmandu 44600, Bagmati, C</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>divshbhai2007@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>02:27 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Hareram Pandit</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>L55-3</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>85.35191</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT15" s="3" t="inlineStr">
-        <is>
-          <t>20h 20m</t>
-        </is>
-      </c>
-      <c r="AU15" s="3" t="inlineStr">
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>4h 41m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV15" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW15" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="AX15" s="3" t="inlineStr">
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX16" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>76.5%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>6</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>47.1%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>11.8%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>29.4%</t>
         </is>
       </c>
     </row>
@@ -838,11 +838,11 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
@@ -851,10 +851,10 @@
         <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>2</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>2</v>
@@ -863,14 +863,14 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0</v>
@@ -888,7 +888,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -898,32 +898,32 @@
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
@@ -1001,13 +1001,13 @@
         <v>5</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" s="4" t="n">
         <v>3</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1021,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX16"/>
+  <dimension ref="A1:AX18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4177,20 +4177,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M16" s="3" t="inlineStr"/>
       <c r="N16" s="3" t="inlineStr">
         <is>
           <t>Divesh Mainali</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9849444217</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9849444217</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -4284,55 +4278,367 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>L55-3</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>85.35191</t>
-        </is>
+      <c r="AP16" s="3" t="n">
+        <v>85.35191</v>
       </c>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>4h 41m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS16" s="3" t="inlineStr">
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX16" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 12:34 PM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : SSID Auto disabled  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>SSID Auto disabled</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353693</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Man bahadur tamang</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Man bahadur tamang</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9808516075</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 12:34:52 PM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>BKT9808516075</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 10:44:10 AM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 12:34:52 PM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr"/>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Bhaktapur, Bhaktapur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>9803643113@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>11:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Sitaram Adhikari</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>L17-2</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr"/>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : SSID Auto disabled  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT16" s="3" t="inlineStr">
-        <is>
-          <t>4h 41m</t>
-        </is>
-      </c>
-      <c r="AU16" s="3" t="inlineStr">
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 50m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV16" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW16" s="3" t="inlineStr">
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : SSID Auto disabled  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX17" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 12:36 PM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr"/>
+      <c r="K18" s="3" t="inlineStr"/>
+      <c r="L18" s="3" t="inlineStr"/>
+      <c r="M18" s="3" t="inlineStr"/>
+      <c r="N18" s="3" t="inlineStr"/>
+      <c r="O18" s="3" t="inlineStr"/>
+      <c r="P18" s="3" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr"/>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr"/>
+      <c r="V18" s="3" t="inlineStr"/>
+      <c r="W18" s="3" t="inlineStr"/>
+      <c r="X18" s="3" t="inlineStr"/>
+      <c r="Y18" s="3" t="inlineStr"/>
+      <c r="Z18" s="3" t="inlineStr"/>
+      <c r="AA18" s="3" t="inlineStr"/>
+      <c r="AB18" s="3" t="inlineStr"/>
+      <c r="AC18" s="3" t="inlineStr"/>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr"/>
+      <c r="AF18" s="3" t="inlineStr"/>
+      <c r="AG18" s="3" t="inlineStr"/>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr"/>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr"/>
+      <c r="AM18" s="3" t="inlineStr"/>
+      <c r="AN18" s="3" t="inlineStr"/>
+      <c r="AO18" s="3" t="inlineStr"/>
+      <c r="AP18" s="3" t="inlineStr"/>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX16" s="3" t="inlineStr">
-        <is>
-          <t>Sabin Giri</t>
+      <c r="AX18" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="C7" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="C7" s="4" t="n">
-        <v>13</v>
-      </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>73.9%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>7</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>39.1%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>8.7%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>43.5%</t>
         </is>
       </c>
     </row>
@@ -820,19 +820,19 @@
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -995,19 +995,19 @@
         <v>1</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>5</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1021,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX18"/>
+  <dimension ref="A1:AX24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4393,10 +4393,8 @@
           <t>Man bahadur tamang</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9808516075</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9808516075</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -4486,10 +4484,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
@@ -4500,7 +4496,7 @@
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>Case : SSID Auto disabled  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
@@ -4642,6 +4638,1270 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 12:57 PM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1354001</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Ram siwakoti</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Ram siwakoti</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9849127058</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 12:57:58 PM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>9849127058</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 02:03:44 PM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 12:57:58 PM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t>27.68028</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>Urbana Montessori School,Bhaktapur Road, Madhyapur Thimi 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>ramsir011@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>08:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Bajgain</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>L4-7</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr">
+        <is>
+          <t>85.36338</t>
+        </is>
+      </c>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>22h 54m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX19" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 12:53 PM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353527</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Elina Maharjan</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Elina Maharjan</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9802206622</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 12:53:03 PM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>9802206622</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 08:59:56 AM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 12:53:03 PM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t>27.68315</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>Kupondole Hotel Kutumba, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr">
+        <is>
+          <t>maharjanelina05@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr"/>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>3,12</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>85.31638</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 53m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX20" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 1:00 PM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353940</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Ishwori pandey</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Ishwori pandey</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9861850476</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 12:54:49 PM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>CHB9861850476</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:18:49 PM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 01:00:15 PM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr"/>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>Modern Nepal College - College Sorhakhutte Bahati Pokhari Buddha Tole Marg Kathmandu 44600, Kathmand</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr">
+        <is>
+          <t>9861850476@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>09:42 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>4,3</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr"/>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>23h 41m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX21" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 12:58 PM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353750</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Pradip Shrestha</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Pradip Shrestha</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9851013018</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:17:16 AM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>9851013018</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:17:16 AM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 12:58:36 PM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t>27.72582</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>Gwarko, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr">
+        <is>
+          <t>traiipshrestha74@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr"/>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>CDB535</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr">
+        <is>
+          <t>85.29673</t>
+        </is>
+      </c>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 41m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 41m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 12:54 PM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353940</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Ishwori pandey</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Ishwori pandey</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9861850476</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 12:54:49 PM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>CHB9861850476</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:18:49 PM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 01:00:15 PM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr"/>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>Modern Nepal College - College Sorhakhutte Bahati Pokhari Buddha Tole Marg Kathmandu 44600, Kathmand</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>9861850476@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr">
+        <is>
+          <t>09:42 hour</t>
+        </is>
+      </c>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>4,3</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr"/>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>23h 41m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX23" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 12:48 PM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353940</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Ishwori pandey</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Ishwori pandey</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9861850476</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 12:54:49 PM</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>CHB9861850476</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:18:49 PM</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 01:00:15 PM</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr"/>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>Modern Nepal College - College Sorhakhutte Bahati Pokhari Buddha Tole Marg Kathmandu 44600, Kathmand</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr">
+        <is>
+          <t>9861850476@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr">
+        <is>
+          <t>09:42 hour</t>
+        </is>
+      </c>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>4,3</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr"/>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>5m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>23h 41m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX24" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
@@ -1067,7 +1067,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -4695,20 +4695,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M19" s="3" t="inlineStr"/>
       <c r="N19" s="3" t="inlineStr">
         <is>
           <t>Ram siwakoti</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9849127058</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9849127058</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -4802,25 +4796,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
           <t>L4-7</t>
         </is>
       </c>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>85.36338</t>
-        </is>
+      <c r="AP19" s="3" t="n">
+        <v>85.36338000000001</v>
       </c>
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
@@ -4921,10 +4911,8 @@
           <t>Elina Maharjan</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9802206622</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9802206622</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -5014,25 +5002,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
           <t>3,12</t>
         </is>
       </c>
-      <c r="AP20" s="3" t="inlineStr">
-        <is>
-          <t>85.31638</t>
-        </is>
+      <c r="AP20" s="3" t="n">
+        <v>85.31638</v>
       </c>
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
@@ -5133,10 +5117,8 @@
           <t>Ishwori pandey</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9861850476</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9861850476</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -5226,10 +5208,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
@@ -5240,7 +5220,7 @@
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
@@ -5341,10 +5321,8 @@
           <t>Pradip Shrestha</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9851013018</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9851013018</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -5434,25 +5412,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
           <t>CDB535</t>
         </is>
       </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>85.29673</t>
-        </is>
+      <c r="AP22" s="3" t="n">
+        <v>85.29673</v>
       </c>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
@@ -5553,10 +5527,8 @@
           <t>Ishwori pandey</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9861850476</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9861850476</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -5646,10 +5618,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
@@ -5660,7 +5630,7 @@
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
@@ -5761,10 +5731,8 @@
           <t>Ishwori pandey</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>9861850476</t>
-        </is>
+      <c r="O24" s="3" t="n">
+        <v>9861850476</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -5854,10 +5822,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN24" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
@@ -5868,7 +5834,7 @@
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>90.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>81.8%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>6.1%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -817,35 +817,35 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>0</v>
@@ -863,23 +863,23 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Configuration Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>2</v>
@@ -888,11 +888,11 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -901,10 +901,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>2</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>2</v>
@@ -938,7 +938,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Channel buffering,feeze issue</t>
+          <t>Low Wi-Fi Range on both band</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -948,13 +948,13 @@
         <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>1</v>
@@ -963,7 +963,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
@@ -973,10 +973,10 @@
         <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -986,28 +986,53 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="4" t="n">
+      <c r="B10" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>19</v>
+      <c r="C10" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1021,7 +1046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX24"/>
+  <dimension ref="A1:AX34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1032,7 +1057,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="28" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -1067,7 +1092,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -5868,6 +5893,2142 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 1:17 PM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1354962</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Ratna Parva Parajuli</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Ratna Parva Parajuli</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9861899658</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 01:17:33 PM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>9861899658</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 10:51:04 AM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 01:17:33 PM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr"/>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>Near KMC School, Baneshwor , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr">
+        <is>
+          <t>ratnap4567@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>02:26 hour</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr"/>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>2h 26m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX25" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 2:11 PM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : Range issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>Range issue</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353637</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Shyam Maharjan</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Shyam Maharjan</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>9841617523</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 09:16:32 AM</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>9841617523</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 10:15:52 AM</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:11:02 PM</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t>27.71774</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC26" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr">
+        <is>
+          <t>Near Prime College, Pahikwo Sadak, Kathmandu , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF26" s="3" t="inlineStr">
+        <is>
+          <t>mrznshyam@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG26" s="3" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on both band</t>
+        </is>
+      </c>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr">
+        <is>
+          <t>13:55 hour</t>
+        </is>
+      </c>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr">
+        <is>
+          <t>Bhawana Bista</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>3,1</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr">
+        <is>
+          <t>85.3018</t>
+        </is>
+      </c>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>Case : Range issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>4h 54m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 55m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : Range issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX26" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 2:10 PM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : Range issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Range issue</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353637</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Shyam Maharjan</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Shyam Maharjan</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>9841617523</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 09:16:32 AM</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>9841617523</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 10:15:52 AM</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:11:02 PM</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t>27.71774</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>Near Prime College, Pahikwo Sadak, Kathmandu , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr">
+        <is>
+          <t>mrznshyam@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on both band</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr">
+        <is>
+          <t>13:55 hour</t>
+        </is>
+      </c>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>Bhawana Bista</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>3,1</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr">
+        <is>
+          <t>85.3018</t>
+        </is>
+      </c>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>Case : Range issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>4h 54m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 55m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : Range issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX27" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 2:29 PM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355081</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Kharka Bahadur Limbu</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Kharka Bahadur Limbu</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>9813278994</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:29:53 PM</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>9813278994</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 12:19:06 PM</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:29:53 PM</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
+          <t>27.673587</t>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA28" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC28" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr">
+        <is>
+          <t>Bhaktapur, Gatthghar, woda number , Near Nagaric Hospital , Nepal Telecom, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF28" s="3" t="inlineStr">
+        <is>
+          <t>Minecraftlix62@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG28" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr">
+        <is>
+          <t>02:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>L51-7</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr">
+        <is>
+          <t>85.3741</t>
+        </is>
+      </c>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>2h 10m</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX28" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 1:39 PM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>TKT1354953</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Sudeep Awal</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>Sudeep Awal</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>9843577377</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 01:39:20 PM</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>9843577377</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 10:44:57 AM</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 01:39:20 PM</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
+          <t>27.676439</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr">
+        <is>
+          <t>Near Bagiswori College 09 Bhaktapur , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="inlineStr"/>
+      <c r="AG29" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr"/>
+      <c r="AI29" s="3" t="inlineStr">
+        <is>
+          <t>02:55 hour</t>
+        </is>
+      </c>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>L10-1</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr">
+        <is>
+          <t>85.440726</t>
+        </is>
+      </c>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>2h 54m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX29" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 2:31 PM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353870</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Kalpana KC</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Kalpana KC</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>9841859961</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:31:06 PM</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>9841859961</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:31:06 PM</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:31:42 PM</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr">
+        <is>
+          <t>27.67006</t>
+        </is>
+      </c>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>Kritipur Municipality,Shahid Path, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr">
+        <is>
+          <t>kcrobert101@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG30" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr">
+        <is>
+          <t>12:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>CDB074</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr">
+        <is>
+          <t>85.28277</t>
+        </is>
+      </c>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX30" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 1:06 PM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>For upgradation to wifi6</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>TKT1345296</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Rojan Shrestha</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>Rojan Shrestha</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>9841115011</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:43:22 PM</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>9813880130</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 08:03:40 PM</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 01:06:11 PM</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t>27.69531</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA31" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC31" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr">
+        <is>
+          <t>Next to Gita Store,Chhune Marg,Kathmandu, Kathmandu, Bagmati, Central, Nepal, Bagmati, Central, Nepa</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr">
+        <is>
+          <t>imrozan1849@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG31" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr">
+        <is>
+          <t>15:05 hour</t>
+        </is>
+      </c>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>CDB387</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr">
+        <is>
+          <t>85.29619</t>
+        </is>
+      </c>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>1d 22m</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>7d 17h 2m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX31" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 1:05 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>For upgradation to wifi6</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1345296</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Rojan Shrestha</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Rojan Shrestha</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>9841115011</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:43:22 PM</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>9813880130</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 08:03:40 PM</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 01:06:11 PM</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t>27.69531</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr"/>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>Next to Gita Store,Chhune Marg,Kathmandu, Kathmandu, Bagmati, Central, Nepal, Bagmati, Central, Nepa</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr">
+        <is>
+          <t>imrozan1849@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="3" t="inlineStr">
+        <is>
+          <t>15:05 hour</t>
+        </is>
+      </c>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>CDB387</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>85.29619</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>1d 22m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>7d 17h 2m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX32" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 2:15 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355014</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Phunchhok Tamang</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Phunchhok Tamang</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>9823511253</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:15:50 PM</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>9803217644</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 11:29:09 AM</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:15:50 PM</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
+          <t>27.72291</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA33" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC33" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr">
+        <is>
+          <t>Boudha Near Kumari College, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr"/>
+      <c r="AG33" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr">
+        <is>
+          <t>02:46 hour</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>L46-3</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>85.35869</t>
+        </is>
+      </c>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>2h 46m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX33" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 1:39 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355059</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Ramesh ghimire</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Ramesh ghimire</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>9841307520</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 01:39:34 PM</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>CHB9841307520</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 12:06:19 PM</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 01:39:34 PM</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr"/>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>BP koirala park (Paneku Park) BP koirala park (Paneku Park) - Garden P85Q+RWW ????????? ??? Bhandark</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>rameshgh2770@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr"/>
+      <c r="AI34" s="3" t="inlineStr">
+        <is>
+          <t>01:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>L7-7</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr"/>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>1h 33m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX34" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>9</v>
-      </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>90.9%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>82.4%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>32.4%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>5.9%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>84.2%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>55.9%</t>
         </is>
       </c>
     </row>
@@ -829,10 +829,10 @@
         <v>4</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -1029,10 +1029,10 @@
         <v>7</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1046,7 +1046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX34"/>
+  <dimension ref="A1:AX35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5960,10 +5960,8 @@
           <t>Ratna Parva Parajuli</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9861899658</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9861899658</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -6053,10 +6051,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
@@ -6067,7 +6063,7 @@
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
@@ -6168,10 +6164,8 @@
           <t>Shyam Maharjan</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>9841617523</t>
-        </is>
+      <c r="O26" s="3" t="n">
+        <v>9841617523</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
@@ -6265,25 +6259,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN26" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
           <t>3,1</t>
         </is>
       </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>85.3018</t>
-        </is>
+      <c r="AP26" s="3" t="n">
+        <v>85.3018</v>
       </c>
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>Case : Range issue   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
@@ -6384,10 +6374,8 @@
           <t>Shyam Maharjan</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>9841617523</t>
-        </is>
+      <c r="O27" s="3" t="n">
+        <v>9841617523</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -6481,25 +6469,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN27" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
           <t>3,1</t>
         </is>
       </c>
-      <c r="AP27" s="3" t="inlineStr">
-        <is>
-          <t>85.3018</t>
-        </is>
+      <c r="AP27" s="3" t="n">
+        <v>85.3018</v>
       </c>
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>Case : Range issue   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
@@ -6600,10 +6584,8 @@
           <t>Kharka Bahadur Limbu</t>
         </is>
       </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>9813278994</t>
-        </is>
+      <c r="O28" s="3" t="n">
+        <v>9813278994</v>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
@@ -6697,25 +6679,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN28" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
           <t>L51-7</t>
         </is>
       </c>
-      <c r="AP28" s="3" t="inlineStr">
-        <is>
-          <t>85.3741</t>
-        </is>
+      <c r="AP28" s="3" t="n">
+        <v>85.3741</v>
       </c>
       <c r="AQ28" s="3" t="inlineStr"/>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
@@ -6816,10 +6794,8 @@
           <t>Sudeep Awal</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>9843577377</t>
-        </is>
+      <c r="O29" s="3" t="n">
+        <v>9843577377</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
@@ -6909,25 +6885,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN29" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
           <t>L10-1</t>
         </is>
       </c>
-      <c r="AP29" s="3" t="inlineStr">
-        <is>
-          <t>85.440726</t>
-        </is>
+      <c r="AP29" s="3" t="n">
+        <v>85.440726</v>
       </c>
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
@@ -7028,10 +7000,8 @@
           <t>Kalpana KC</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>9841859961</t>
-        </is>
+      <c r="O30" s="3" t="n">
+        <v>9841859961</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
@@ -7125,25 +7095,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN30" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
           <t>CDB074</t>
         </is>
       </c>
-      <c r="AP30" s="3" t="inlineStr">
-        <is>
-          <t>85.28277</t>
-        </is>
+      <c r="AP30" s="3" t="n">
+        <v>85.28277</v>
       </c>
       <c r="AQ30" s="3" t="inlineStr"/>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
@@ -7244,10 +7210,8 @@
           <t>Rojan Shrestha</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>9841115011</t>
-        </is>
+      <c r="O31" s="3" t="n">
+        <v>9841115011</v>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
@@ -7341,25 +7305,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN31" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
           <t>CDB387</t>
         </is>
       </c>
-      <c r="AP31" s="3" t="inlineStr">
-        <is>
-          <t>85.29619</t>
-        </is>
+      <c r="AP31" s="3" t="n">
+        <v>85.29619</v>
       </c>
       <c r="AQ31" s="3" t="inlineStr"/>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
@@ -7460,10 +7420,8 @@
           <t>Rojan Shrestha</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>9841115011</t>
-        </is>
+      <c r="O32" s="3" t="n">
+        <v>9841115011</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
@@ -7557,25 +7515,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN32" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
           <t>CDB387</t>
         </is>
       </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>85.29619</t>
-        </is>
+      <c r="AP32" s="3" t="n">
+        <v>85.29619</v>
       </c>
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
@@ -7676,10 +7630,8 @@
           <t>Phunchhok Tamang</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>9823511253</t>
-        </is>
+      <c r="O33" s="3" t="n">
+        <v>9823511253</v>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
@@ -7769,25 +7721,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN33" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
           <t>L46-3</t>
         </is>
       </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>85.35869</t>
-        </is>
+      <c r="AP33" s="3" t="n">
+        <v>85.35869</v>
       </c>
       <c r="AQ33" s="3" t="inlineStr"/>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
@@ -7888,10 +7836,8 @@
           <t>Ramesh ghimire</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>9841307520</t>
-        </is>
+      <c r="O34" s="3" t="n">
+        <v>9841307520</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
@@ -7981,10 +7927,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN34" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
@@ -7995,29 +7939,29 @@
       <c r="AQ34" s="3" t="inlineStr"/>
       <c r="AR34" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>1h 33m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS34" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT34" s="3" t="inlineStr">
-        <is>
-          <t>1h 33m</t>
-        </is>
-      </c>
-      <c r="AU34" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV34" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="AW34" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -8026,6 +7970,218 @@
       <c r="AX34" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 2:59 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353799</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Bijay Chaudhary</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>Bijay Chaudhary</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>9817684819</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:44:48 AM</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>9817684819</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:44:48 AM</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:59:42 PM</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr">
+        <is>
+          <t>27.69618</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA35" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC35" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu Municipality-14,Laxmi Tole, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr"/>
+      <c r="AG35" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr"/>
+      <c r="AI35" s="3" t="inlineStr">
+        <is>
+          <t>13:15 hour</t>
+        </is>
+      </c>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr">
+        <is>
+          <t>Sandesh Ghale</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>1,16</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>85.27952</t>
+        </is>
+      </c>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 14m</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 14m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX35" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>82.9%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>31.4%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>5.7%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -826,13 +826,13 @@
         <v>5</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>4</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -1026,13 +1026,13 @@
         <v>7</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>7</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1046,7 +1046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX35"/>
+  <dimension ref="A1:AX36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1059,10 +1059,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="35" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="35" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -8040,10 +8040,8 @@
           <t>Bijay Chaudhary</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>9817684819</t>
-        </is>
+      <c r="O35" s="3" t="n">
+        <v>9817684819</v>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
@@ -8133,47 +8131,43 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN35" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
           <t>1,16</t>
         </is>
       </c>
-      <c r="AP35" s="3" t="inlineStr">
-        <is>
-          <t>85.27952</t>
-        </is>
+      <c r="AP35" s="3" t="n">
+        <v>85.27952000000001</v>
       </c>
       <c r="AQ35" s="3" t="inlineStr"/>
       <c r="AR35" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 14m</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 14m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS35" s="3" t="inlineStr">
-        <is>
-          <t>1d 3h 14m</t>
-        </is>
-      </c>
-      <c r="AT35" s="3" t="inlineStr">
-        <is>
-          <t>1d 3h 14m</t>
-        </is>
-      </c>
-      <c r="AU35" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV35" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW35" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -8182,6 +8176,222 @@
       <c r="AX35" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 2:58 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355090</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Bhagawati Media creation pvt ltd</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Bhagawati Media creation pvt ltd</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>9851091254</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:58:29 PM</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>9851091254</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 12:21:54 PM</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:58:29 PM</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t>27.67574</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr">
+        <is>
+          <t>Koteshwor Near koteshwor bhatbhateni supermarket n Prabhu bank, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr">
+        <is>
+          <t>bhagwati.media89@yahoo.com</t>
+        </is>
+      </c>
+      <c r="AG36" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr"/>
+      <c r="AI36" s="3" t="inlineStr">
+        <is>
+          <t>02:37 hour</t>
+        </is>
+      </c>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr">
+        <is>
+          <t>85.34686</t>
+        </is>
+      </c>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>2h 36m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX36" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>6</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>82.9%</t>
+          <t>81.1%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>10</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>32.4%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>5.4%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>54.1%</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -863,11 +863,11 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
@@ -876,10 +876,10 @@
         <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>2</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>2</v>
@@ -888,11 +888,11 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -901,10 +901,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>2</v>
@@ -913,7 +913,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Low Wi-Fi Range on both band</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -938,7 +938,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on both band</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -948,13 +948,13 @@
         <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>1</v>
@@ -963,7 +963,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Channel buffering,feeze issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
@@ -988,7 +988,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -998,10 +998,10 @@
         <v>0</v>
       </c>
       <c r="D9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -1011,28 +1011,53 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B11" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C11" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="E10" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>29</v>
+      <c r="G11" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1046,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX36"/>
+  <dimension ref="A1:AX38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8246,10 +8271,8 @@
           <t>Bhagawati Media creation pvt ltd</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>9851091254</t>
-        </is>
+      <c r="O36" s="3" t="n">
+        <v>9851091254</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
@@ -8343,55 +8366,371 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN36" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
           <t>2,3</t>
         </is>
       </c>
-      <c r="AP36" s="3" t="inlineStr">
-        <is>
-          <t>85.34686</t>
-        </is>
+      <c r="AP36" s="3" t="n">
+        <v>85.34686000000001</v>
       </c>
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>2h 36m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS36" s="3" t="inlineStr">
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX36" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 3:23 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>STB issue</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350105</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Sarita Kumari Dunjan Tamang</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Sarita Kumari Dunjan Tamang</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>9803201390</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 03:23:22 PM</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>9803201390</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 02:28:28 PM</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 03:23:22 PM</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr">
+        <is>
+          <t>27.71816</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC37" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr">
+        <is>
+          <t>Taragaon, Kathmandu 44601 Near by Hyatt Regency Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr"/>
+      <c r="AG37" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr"/>
+      <c r="AI37" s="3" t="inlineStr">
+        <is>
+          <t>16:55 hour</t>
+        </is>
+      </c>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Nepali</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>L2-8</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>85.35434</t>
+        </is>
+      </c>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT36" s="3" t="inlineStr">
-        <is>
-          <t>2h 36m</t>
-        </is>
-      </c>
-      <c r="AU36" s="3" t="inlineStr">
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>4d 54m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV36" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW36" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
-        </is>
-      </c>
-      <c r="AX36" s="3" t="inlineStr">
-        <is>
-          <t>Shashikant Chaudhary</t>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX37" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 3:24 PM</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : router  damage   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr"/>
+      <c r="J38" s="3" t="inlineStr"/>
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="3" t="inlineStr"/>
+      <c r="M38" s="3" t="inlineStr"/>
+      <c r="N38" s="3" t="inlineStr"/>
+      <c r="O38" s="3" t="inlineStr"/>
+      <c r="P38" s="3" t="inlineStr"/>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr"/>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr"/>
+      <c r="V38" s="3" t="inlineStr"/>
+      <c r="W38" s="3" t="inlineStr"/>
+      <c r="X38" s="3" t="inlineStr"/>
+      <c r="Y38" s="3" t="inlineStr"/>
+      <c r="Z38" s="3" t="inlineStr"/>
+      <c r="AA38" s="3" t="inlineStr"/>
+      <c r="AB38" s="3" t="inlineStr"/>
+      <c r="AC38" s="3" t="inlineStr"/>
+      <c r="AD38" s="3" t="inlineStr"/>
+      <c r="AE38" s="3" t="inlineStr"/>
+      <c r="AF38" s="3" t="inlineStr"/>
+      <c r="AG38" s="3" t="inlineStr"/>
+      <c r="AH38" s="3" t="inlineStr"/>
+      <c r="AI38" s="3" t="inlineStr"/>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr"/>
+      <c r="AM38" s="3" t="inlineStr"/>
+      <c r="AN38" s="3" t="inlineStr"/>
+      <c r="AO38" s="3" t="inlineStr"/>
+      <c r="AP38" s="3" t="inlineStr"/>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>Case : router  damage   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX38" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>82.1%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>11</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>5.1%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>53.8%</t>
         </is>
       </c>
     </row>
@@ -820,19 +820,19 @@
         <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>5</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>4</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -1045,19 +1045,19 @@
         <v>3</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>8</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>7</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX38"/>
+  <dimension ref="A1:AX40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1105,7 +1105,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="29" customWidth="1" min="32" max="32"/>
+    <col width="32" customWidth="1" min="32" max="32"/>
     <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -8481,10 +8481,8 @@
           <t>Sarita Kumari Dunjan Tamang</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>9803201390</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>9803201390</v>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -8574,25 +8572,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN37" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
           <t>L2-8</t>
         </is>
       </c>
-      <c r="AP37" s="3" t="inlineStr">
-        <is>
-          <t>85.35434</t>
-        </is>
+      <c r="AP37" s="3" t="n">
+        <v>85.35433999999999</v>
       </c>
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>Case : STB issue   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
@@ -8734,6 +8728,426 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 3:44 PM</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrad   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>router upgrad</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>TKT1354137</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Balkrishna Maharjan</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>Balkrishna Maharjan</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>9841380913</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 03:44:15 PM</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>9841380913</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:09:19 PM</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 03:44:15 PM</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr"/>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA39" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB39" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC39" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur	Tikathalli budda colony, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF39" s="3" t="inlineStr"/>
+      <c r="AG39" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr">
+        <is>
+          <t>09:35 hour</t>
+        </is>
+      </c>
+      <c r="AJ39" s="3" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>4,13</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr"/>
+      <c r="AQ39" s="3" t="inlineStr"/>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrad   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>23h 34m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrad   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX39" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 3:46 PM</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355141</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>Sushant Sharma</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Sushant Sharma</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>9808635117</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 03:46:07 PM</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>9808635117</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 12:43:43 PM</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 03:46:07 PM</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr">
+        <is>
+          <t>27.6925</t>
+        </is>
+      </c>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA40" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB40" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC40" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD40" s="3" t="inlineStr"/>
+      <c r="AE40" s="3" t="inlineStr">
+        <is>
+          <t>Balkhu Near lions club pvt. ltd., Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF40" s="3" t="inlineStr">
+        <is>
+          <t>sushant.sharma123@hotmail.com</t>
+        </is>
+      </c>
+      <c r="AG40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH40" s="3" t="inlineStr"/>
+      <c r="AI40" s="3" t="inlineStr">
+        <is>
+          <t>03:03 hour</t>
+        </is>
+      </c>
+      <c r="AJ40" s="3" t="inlineStr"/>
+      <c r="AK40" s="3" t="inlineStr"/>
+      <c r="AL40" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO40" s="3" t="inlineStr">
+        <is>
+          <t>3,13</t>
+        </is>
+      </c>
+      <c r="AP40" s="3" t="inlineStr">
+        <is>
+          <t>85.31493</t>
+        </is>
+      </c>
+      <c r="AQ40" s="3" t="inlineStr"/>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>3h 2m</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX40" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>7</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>82.5%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>32.5%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>5.0%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>86.4%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>55.0%</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
         <v>4</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>6</v>
@@ -832,7 +832,7 @@
         <v>4</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -1048,7 +1048,7 @@
         <v>5</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>9</v>
@@ -1057,7 +1057,7 @@
         <v>7</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX40"/>
+  <dimension ref="A1:AX41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8795,10 +8795,8 @@
           <t>Balkrishna Maharjan</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>9841380913</t>
-        </is>
+      <c r="O39" s="3" t="n">
+        <v>9841380913</v>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
@@ -8884,10 +8882,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN39" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
@@ -8898,7 +8894,7 @@
       <c r="AQ39" s="3" t="inlineStr"/>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrad   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
@@ -8999,10 +8995,8 @@
           <t>Sushant Sharma</t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>9808635117</t>
-        </is>
+      <c r="O40" s="3" t="n">
+        <v>9808635117</v>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
@@ -9096,55 +9090,267 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN40" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN40" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
           <t>3,13</t>
         </is>
       </c>
-      <c r="AP40" s="3" t="inlineStr">
-        <is>
-          <t>85.31493</t>
-        </is>
+      <c r="AP40" s="3" t="n">
+        <v>85.31493</v>
       </c>
       <c r="AQ40" s="3" t="inlineStr"/>
       <c r="AR40" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>3h 2m</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS40" s="3" t="inlineStr">
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX40" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 3:58 PM</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355146</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Navin Awal</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>Navin Awal</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>9841225726</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 03:58:42 PM</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>9841225726</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 12:44:33 PM</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 03:58:42 PM</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t>27.68862</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA41" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB41" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC41" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD41" s="3" t="inlineStr"/>
+      <c r="AE41" s="3" t="inlineStr">
+        <is>
+          <t>Bhaktapur Pepsicola Namuna garden Home Zone Garden F89, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF41" s="3" t="inlineStr">
+        <is>
+          <t>navinawal@hotmail.com</t>
+        </is>
+      </c>
+      <c r="AG41" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH41" s="3" t="inlineStr"/>
+      <c r="AI41" s="3" t="inlineStr">
+        <is>
+          <t>03:14 hour</t>
+        </is>
+      </c>
+      <c r="AJ41" s="3" t="inlineStr"/>
+      <c r="AK41" s="3" t="inlineStr"/>
+      <c r="AL41" s="3" t="inlineStr">
+        <is>
+          <t>Sameer Thapa</t>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>L10-5</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr">
+        <is>
+          <t>85.36339</t>
+        </is>
+      </c>
+      <c r="AQ41" s="3" t="inlineStr"/>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT40" s="3" t="inlineStr">
-        <is>
-          <t>3h 2m</t>
-        </is>
-      </c>
-      <c r="AU40" s="3" t="inlineStr">
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>3h 14m</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV40" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW40" s="3" t="inlineStr">
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW41" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX40" s="3" t="inlineStr">
-        <is>
-          <t>Rajesh Maharjan</t>
+      <c r="AX41" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>82.5%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>12</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>4.8%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>87.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.8%</t>
         </is>
       </c>
     </row>
@@ -826,13 +826,13 @@
         <v>6</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>4</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -913,11 +913,11 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on both band</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
@@ -926,13 +926,13 @@
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="G6" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -988,7 +988,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Channel buffering,feeze issue</t>
+          <t>Low Wi-Fi Range on both band</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -998,13 +998,13 @@
         <v>0</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -1023,10 +1023,10 @@
         <v>0</v>
       </c>
       <c r="D10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0</v>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>5</v>
@@ -1051,13 +1051,13 @@
         <v>9</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>7</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX41"/>
+  <dimension ref="A1:AX43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -9205,10 +9205,8 @@
           <t>Navin Awal</t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>9841225726</t>
-        </is>
+      <c r="O41" s="3" t="n">
+        <v>9841225726</v>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
@@ -9302,55 +9300,471 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN41" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
           <t>L10-5</t>
         </is>
       </c>
-      <c r="AP41" s="3" t="inlineStr">
-        <is>
-          <t>85.36339</t>
-        </is>
+      <c r="AP41" s="3" t="n">
+        <v>85.36339</v>
       </c>
       <c r="AQ41" s="3" t="inlineStr"/>
       <c r="AR41" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>3h 14m</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS41" s="3" t="inlineStr">
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX41" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 4:13 PM</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1354706</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>santosh shah</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>santosh shah</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>9819865226</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 04:13:13 PM</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>9819865226</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 06:42:54 AM</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 04:13:13 PM</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="inlineStr"/>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA42" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB42" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC42" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD42" s="3" t="inlineStr"/>
+      <c r="AE42" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur	imadol,suryanagar tole, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF42" s="3" t="inlineStr"/>
+      <c r="AG42" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH42" s="3" t="inlineStr"/>
+      <c r="AI42" s="3" t="inlineStr">
+        <is>
+          <t>06:13 hour</t>
+        </is>
+      </c>
+      <c r="AJ42" s="3" t="inlineStr"/>
+      <c r="AK42" s="3" t="inlineStr"/>
+      <c r="AL42" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>L47-5</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr"/>
+      <c r="AQ42" s="3" t="inlineStr"/>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT41" s="3" t="inlineStr">
-        <is>
-          <t>3h 14m</t>
-        </is>
-      </c>
-      <c r="AU41" s="3" t="inlineStr">
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>9h 30m</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV41" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW41" s="3" t="inlineStr">
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW42" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX41" s="3" t="inlineStr">
-        <is>
-          <t>Sabin Giri</t>
+      <c r="AX42" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 4:08 PM</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Case : net slow   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>net slow</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>TKT1354878</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Shandaar Mo:Mo Balkhu</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>Shandaar Mo:Mo Balkhu</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>9747821804</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 04:08:31 PM</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>KLK9747821804</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 10:00:49 AM</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 04:08:31 PM</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA43" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB43" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC43" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD43" s="3" t="inlineStr"/>
+      <c r="AE43" s="3" t="inlineStr">
+        <is>
+          <t>Balkhu, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF43" s="3" t="inlineStr">
+        <is>
+          <t>9747821804@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG43" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH43" s="3" t="inlineStr"/>
+      <c r="AI43" s="3" t="inlineStr">
+        <is>
+          <t>06:08 hour</t>
+        </is>
+      </c>
+      <c r="AJ43" s="3" t="inlineStr"/>
+      <c r="AK43" s="3" t="inlineStr"/>
+      <c r="AL43" s="3" t="inlineStr">
+        <is>
+          <t>Bhaskar Pant</t>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>CDB145</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ43" s="3" t="inlineStr"/>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>Case : net slow   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>6h 7m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
+          <t>Case : net slow   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX43" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>8</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>90.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>83.7%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>13</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.9%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>4.7%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>53.5%</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
         <v>4</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>7</v>
@@ -832,7 +832,7 @@
         <v>4</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -1048,7 +1048,7 @@
         <v>5</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>10</v>
@@ -1057,7 +1057,7 @@
         <v>7</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX43"/>
+  <dimension ref="A1:AX44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -9415,10 +9415,8 @@
           <t>santosh shah</t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>9819865226</t>
-        </is>
+      <c r="O42" s="3" t="n">
+        <v>9819865226</v>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
@@ -9504,10 +9502,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN42" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
@@ -9518,7 +9514,7 @@
       <c r="AQ42" s="3" t="inlineStr"/>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
@@ -9619,10 +9615,8 @@
           <t>Shandaar Mo:Mo Balkhu</t>
         </is>
       </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>9747821804</t>
-        </is>
+      <c r="O43" s="3" t="n">
+        <v>9747821804</v>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
@@ -9716,55 +9710,267 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN43" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
           <t>CDB145</t>
         </is>
       </c>
-      <c r="AP43" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP43" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ43" s="3" t="inlineStr"/>
       <c r="AR43" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>6h 7m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
           <t>Case : net slow   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS43" s="3" t="inlineStr">
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX43" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 4:19 PM</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1354973</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>Meena Kumari Tamang</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>Meena Kumari Tamang</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>9841387613</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 04:19:55 PM</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t>9841387613</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 11:01:32 AM</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 04:19:55 PM</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr">
+        <is>
+          <t>27.6979</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA44" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB44" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC44" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD44" s="3" t="inlineStr"/>
+      <c r="AE44" s="3" t="inlineStr">
+        <is>
+          <t>near Good Day Academy, M9XF+428, Kageshwari Manohara 44600. Ward no  9, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF44" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG44" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH44" s="3" t="inlineStr"/>
+      <c r="AI44" s="3" t="inlineStr">
+        <is>
+          <t>05:18 hour</t>
+        </is>
+      </c>
+      <c r="AJ44" s="3" t="inlineStr"/>
+      <c r="AK44" s="3" t="inlineStr"/>
+      <c r="AL44" s="3" t="inlineStr">
+        <is>
+          <t>Gaurab Dahal</t>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO44" s="3" t="inlineStr">
+        <is>
+          <t>L34-2</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr">
+        <is>
+          <t>85.37196</t>
+        </is>
+      </c>
+      <c r="AQ44" s="3" t="inlineStr"/>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT43" s="3" t="inlineStr">
-        <is>
-          <t>6h 7m</t>
-        </is>
-      </c>
-      <c r="AU43" s="3" t="inlineStr">
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>5h 18m</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV43" s="3" t="inlineStr">
-        <is>
-          <t>Case : net slow   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="AW43" s="3" t="inlineStr">
+      <c r="AV44" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW44" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AX43" s="3" t="inlineStr">
-        <is>
-          <t>Ajit Shrestha</t>
+      <c r="AX44" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
@@ -1117,7 +1117,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -9825,10 +9825,8 @@
           <t>Meena Kumari Tamang</t>
         </is>
       </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>9841387613</t>
-        </is>
+      <c r="O44" s="3" t="n">
+        <v>9841387613</v>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
@@ -9922,25 +9920,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN44" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
           <t>L34-2</t>
         </is>
       </c>
-      <c r="AP44" s="3" t="inlineStr">
-        <is>
-          <t>85.37196</t>
-        </is>
+      <c r="AP44" s="3" t="n">
+        <v>85.37196</v>
       </c>
       <c r="AQ44" s="3" t="inlineStr"/>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>8</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>36</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>83.7%</t>
+          <t>81.8%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>14</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>36.4%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>4.5%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>52.3%</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX44"/>
+  <dimension ref="A1:AX45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1117,7 +1117,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -9968,6 +9968,218 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 5:00 PM</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Case : worst internet service   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>worst internet service</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350654</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Shrestha</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Shrestha</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>9700971170</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 09:53:45 PM</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t>9823190890R</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 07:40:24 PM</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 05:00:45 PM</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t>27.66368,</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA45" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC45" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD45" s="3" t="inlineStr">
+        <is>
+          <t>Box End</t>
+        </is>
+      </c>
+      <c r="AE45" s="3" t="inlineStr">
+        <is>
+          <t>ala Futsal &amp; Recreational Center Details from Google Maps Unnamed Road, M87P+5VQ, ?????????? 44700 +</t>
+        </is>
+      </c>
+      <c r="AF45" s="3" t="inlineStr">
+        <is>
+          <t>rs1460451@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG45" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH45" s="3" t="inlineStr"/>
+      <c r="AI45" s="3" t="inlineStr"/>
+      <c r="AJ45" s="3" t="inlineStr"/>
+      <c r="AK45" s="3" t="inlineStr"/>
+      <c r="AL45" s="3" t="inlineStr"/>
+      <c r="AM45" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO45" s="3" t="inlineStr">
+        <is>
+          <t>1,15</t>
+        </is>
+      </c>
+      <c r="AP45" s="3" t="inlineStr">
+        <is>
+          <t>85.33794</t>
+        </is>
+      </c>
+      <c r="AQ45" s="3" t="inlineStr"/>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>Case : worst internet service   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>1d 19h 7m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>3d 21h 20m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
+          <t>Case : worst internet service   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX45" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>82.6%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>34.8%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>4.3%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>87.0%</t>
+          <t>88.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>54.3%</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>4</v>
@@ -832,7 +832,7 @@
         <v>4</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>5</v>
@@ -1057,7 +1057,7 @@
         <v>7</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX45"/>
+  <dimension ref="A1:AX47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10035,10 +10035,8 @@
           <t>Roshan Shrestha</t>
         </is>
       </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>9700971170</t>
-        </is>
+      <c r="O45" s="3" t="n">
+        <v>9700971170</v>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
@@ -10128,47 +10126,43 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN45" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN45" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
           <t>1,15</t>
         </is>
       </c>
-      <c r="AP45" s="3" t="inlineStr">
-        <is>
-          <t>85.33794</t>
-        </is>
+      <c r="AP45" s="3" t="n">
+        <v>85.33794</v>
       </c>
       <c r="AQ45" s="3" t="inlineStr"/>
       <c r="AR45" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>1d 19h 7m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>3d 21h 20m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
           <t>Case : worst internet service   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS45" s="3" t="inlineStr">
-        <is>
-          <t>1d 19h 7m</t>
-        </is>
-      </c>
-      <c r="AT45" s="3" t="inlineStr">
-        <is>
-          <t>3d 21h 20m</t>
-        </is>
-      </c>
-      <c r="AU45" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV45" s="3" t="inlineStr">
-        <is>
-          <t>Case : worst internet service   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW45" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -10177,6 +10171,438 @@
       <c r="AX45" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 5:02 PM</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355210</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>Dilli Tamang</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>Dilli Tamang</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>9808211683</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 01:11:08 PM</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>9808211683</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 01:11:08 PM</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 05:02:52 PM</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t>27.70826</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA46" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB46" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC46" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD46" s="3" t="inlineStr"/>
+      <c r="AE46" s="3" t="inlineStr">
+        <is>
+          <t>Near to Cheese world nepalaya , Dallu , Kathmandu , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF46" s="3" t="inlineStr">
+        <is>
+          <t>dillitamang27@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG46" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH46" s="3" t="inlineStr"/>
+      <c r="AI46" s="3" t="inlineStr">
+        <is>
+          <t>03:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ46" s="3" t="inlineStr"/>
+      <c r="AK46" s="3" t="inlineStr"/>
+      <c r="AL46" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO46" s="3" t="inlineStr">
+        <is>
+          <t>CDB347</t>
+        </is>
+      </c>
+      <c r="AP46" s="3" t="inlineStr">
+        <is>
+          <t>85.30218</t>
+        </is>
+      </c>
+      <c r="AQ46" s="3" t="inlineStr"/>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>3h 51m</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>3h 51m</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW46" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX46" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 5:01 PM</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355210</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>Dilli Tamang</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>Dilli Tamang</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>9808211683</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 01:11:08 PM</t>
+        </is>
+      </c>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr">
+        <is>
+          <t>9808211683</t>
+        </is>
+      </c>
+      <c r="V47" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 01:11:08 PM</t>
+        </is>
+      </c>
+      <c r="W47" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 05:02:52 PM</t>
+        </is>
+      </c>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y47" s="3" t="inlineStr">
+        <is>
+          <t>27.70826</t>
+        </is>
+      </c>
+      <c r="Z47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA47" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB47" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC47" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD47" s="3" t="inlineStr"/>
+      <c r="AE47" s="3" t="inlineStr">
+        <is>
+          <t>Near to Cheese world nepalaya , Dallu , Kathmandu , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF47" s="3" t="inlineStr">
+        <is>
+          <t>dillitamang27@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG47" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH47" s="3" t="inlineStr"/>
+      <c r="AI47" s="3" t="inlineStr">
+        <is>
+          <t>03:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ47" s="3" t="inlineStr"/>
+      <c r="AK47" s="3" t="inlineStr"/>
+      <c r="AL47" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN47" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO47" s="3" t="inlineStr">
+        <is>
+          <t>CDB347</t>
+        </is>
+      </c>
+      <c r="AP47" s="3" t="inlineStr">
+        <is>
+          <t>85.30218</t>
+        </is>
+      </c>
+      <c r="AQ47" s="3" t="inlineStr"/>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>3h 51m</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>3h 51m</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>83.0%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>34.0%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>88.5%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>55.3%</t>
         </is>
       </c>
     </row>
@@ -826,13 +826,13 @@
         <v>7</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>4</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -1051,13 +1051,13 @@
         <v>10</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>7</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX47"/>
+  <dimension ref="A1:AX48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10241,10 +10241,8 @@
           <t>Dilli Tamang</t>
         </is>
       </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>9808211683</t>
-        </is>
+      <c r="O46" s="3" t="n">
+        <v>9808211683</v>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
@@ -10338,25 +10336,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN46" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN46" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
           <t>CDB347</t>
         </is>
       </c>
-      <c r="AP46" s="3" t="inlineStr">
-        <is>
-          <t>85.30218</t>
-        </is>
+      <c r="AP46" s="3" t="n">
+        <v>85.30218000000001</v>
       </c>
       <c r="AQ46" s="3" t="inlineStr"/>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
@@ -10457,10 +10451,8 @@
           <t>Dilli Tamang</t>
         </is>
       </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>9808211683</t>
-        </is>
+      <c r="O47" s="3" t="n">
+        <v>9808211683</v>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
@@ -10554,47 +10546,43 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN47" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN47" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
           <t>CDB347</t>
         </is>
       </c>
-      <c r="AP47" s="3" t="inlineStr">
-        <is>
-          <t>85.30218</t>
-        </is>
+      <c r="AP47" s="3" t="n">
+        <v>85.30218000000001</v>
       </c>
       <c r="AQ47" s="3" t="inlineStr"/>
       <c r="AR47" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>3h 51m</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>3h 51m</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
           <t>Case : upgrade wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS47" s="3" t="inlineStr">
-        <is>
-          <t>3h 51m</t>
-        </is>
-      </c>
-      <c r="AT47" s="3" t="inlineStr">
-        <is>
-          <t>3h 51m</t>
-        </is>
-      </c>
-      <c r="AU47" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV47" s="3" t="inlineStr">
-        <is>
-          <t>Case : upgrade wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW47" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -10603,6 +10591,222 @@
       <c r="AX47" s="3" t="inlineStr">
         <is>
           <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 5:28 PM</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>WIFI6 Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355356</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>Bishwaraj Gautam</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>Bishwaraj Gautam</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>9761804700</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr"/>
+      <c r="R48" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 05:28:52 PM</t>
+        </is>
+      </c>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr">
+        <is>
+          <t>9761804700</t>
+        </is>
+      </c>
+      <c r="V48" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:05:34 PM</t>
+        </is>
+      </c>
+      <c r="W48" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 05:28:52 PM</t>
+        </is>
+      </c>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y48" s="3" t="inlineStr">
+        <is>
+          <t>27.677992</t>
+        </is>
+      </c>
+      <c r="Z48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA48" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB48" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC48" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD48" s="3" t="inlineStr"/>
+      <c r="AE48" s="3" t="inlineStr">
+        <is>
+          <t>Advance oral dental hospital - Emergency dental service Saraswati Marga Kathmandu 44600, Bagmati, Ce</t>
+        </is>
+      </c>
+      <c r="AF48" s="3" t="inlineStr">
+        <is>
+          <t>biswarajgautam8@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG48" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH48" s="3" t="inlineStr"/>
+      <c r="AI48" s="3" t="inlineStr">
+        <is>
+          <t>03:23 hour</t>
+        </is>
+      </c>
+      <c r="AJ48" s="3" t="inlineStr"/>
+      <c r="AK48" s="3" t="inlineStr"/>
+      <c r="AL48" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM48" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN48" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO48" s="3" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="AP48" s="3" t="inlineStr">
+        <is>
+          <t>85.347003</t>
+        </is>
+      </c>
+      <c r="AQ48" s="3" t="inlineStr"/>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>3h 23m</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX48" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
@@ -1117,7 +1117,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -10661,10 +10661,8 @@
           <t>Bishwaraj Gautam</t>
         </is>
       </c>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
-          <t>9761804700</t>
-        </is>
+      <c r="O48" s="3" t="n">
+        <v>9761804700</v>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
@@ -10758,25 +10756,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN48" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN48" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
           <t>1,4</t>
         </is>
       </c>
-      <c r="AP48" s="3" t="inlineStr">
-        <is>
-          <t>85.347003</t>
-        </is>
+      <c r="AP48" s="3" t="n">
+        <v>85.347003</v>
       </c>
       <c r="AQ48" s="3" t="inlineStr"/>
       <c r="AR48" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Router Upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS48" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>76.9%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>83.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.2%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>35.4%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>54.2%</t>
         </is>
       </c>
     </row>
@@ -826,13 +826,13 @@
         <v>7</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>4</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -1051,13 +1051,13 @@
         <v>10</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>7</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX48"/>
+  <dimension ref="A1:AX49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1117,7 +1117,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -10804,6 +10804,222 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 6:06 PM</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Case : router exchange related  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>router exchange related</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355573</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>Kumar Thapa</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>Kumar Thapa</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>9823148870</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 06:06:32 PM</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>9823148870</t>
+        </is>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 04:07:16 PM</t>
+        </is>
+      </c>
+      <c r="W49" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 06:06:32 PM</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y49" s="3" t="inlineStr">
+        <is>
+          <t>27.66511</t>
+        </is>
+      </c>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA49" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC49" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD49" s="3" t="inlineStr"/>
+      <c r="AE49" s="3" t="inlineStr">
+        <is>
+          <t>Imadol Garkhuw krishna mandir - Hope Valley School,M89V+6QW, Mahalaxmi 44600, Lalitpur, Bagmati, Nep</t>
+        </is>
+      </c>
+      <c r="AF49" s="3" t="inlineStr">
+        <is>
+          <t>thapkumar10000@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG49" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH49" s="3" t="inlineStr"/>
+      <c r="AI49" s="3" t="inlineStr">
+        <is>
+          <t>01:59 hour</t>
+        </is>
+      </c>
+      <c r="AJ49" s="3" t="inlineStr"/>
+      <c r="AK49" s="3" t="inlineStr"/>
+      <c r="AL49" s="3" t="inlineStr">
+        <is>
+          <t>Anisha Khadka</t>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO49" s="3" t="inlineStr">
+        <is>
+          <t>CDB412</t>
+        </is>
+      </c>
+      <c r="AP49" s="3" t="inlineStr">
+        <is>
+          <t>85.34544</t>
+        </is>
+      </c>
+      <c r="AQ49" s="3" t="inlineStr"/>
+      <c r="AR49" s="3" t="inlineStr">
+        <is>
+          <t>Case : router exchange related  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>1h 59m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
+          <t>Case : router exchange related  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX49" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_02_Oct_2026.xlsx
@@ -1117,7 +1117,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -10871,10 +10871,8 @@
           <t>Kumar Thapa</t>
         </is>
       </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
-          <t>9823148870</t>
-        </is>
+      <c r="O49" s="3" t="n">
+        <v>9823148870</v>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
@@ -10968,25 +10966,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN49" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN49" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
           <t>CDB412</t>
         </is>
       </c>
-      <c r="AP49" s="3" t="inlineStr">
-        <is>
-          <t>85.34544</t>
-        </is>
+      <c r="AP49" s="3" t="n">
+        <v>85.34544</v>
       </c>
       <c r="AQ49" s="3" t="inlineStr"/>
       <c r="AR49" s="3" t="inlineStr">
         <is>
-          <t>Case : router exchange related  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS49" s="3" t="inlineStr">
